--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ139"/>
+  <dimension ref="A1:AZ140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98347056</v>
+        <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>92564</v>
+        <v>88605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>1008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -828,21 +828,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sessön, ö delen, Upl</t>
+          <t>Långgarn, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711041</v>
+        <v>710972</v>
       </c>
       <c r="R3" t="n">
-        <v>6631123</v>
+        <v>6631272</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,53 +869,62 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tre meter hög kapad granhlgstubbe 2 m öster om grusväg.</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Anna  Engqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Lars-Åke Gisselson</t>
+          <t>Anna  Engqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98347056</t>
+          <t>https://artportalen.se/Sighting/136875884</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73165004</v>
+        <v>98347056</v>
       </c>
       <c r="B4" t="n">
-        <v>96437</v>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +932,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, ö delen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710916</v>
+        <v>711041</v>
       </c>
       <c r="R4" t="n">
-        <v>6631188</v>
+        <v>6631123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +997,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tre meter hög kapad granhlgstubbe 2 m öster om grusväg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,33 +1016,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Kristoffer Stighäll, Lars-Åke Gisselson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165004</t>
+          <t>https://artportalen.se/Sighting/98347056</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73164986</v>
+        <v>73165004</v>
       </c>
       <c r="B5" t="n">
-        <v>96426</v>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710998</v>
+        <v>710916</v>
       </c>
       <c r="R5" t="n">
-        <v>6631300</v>
+        <v>6631188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,16 +1136,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164986</t>
+          <t>https://artportalen.se/Sighting/73165004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121266777</v>
+        <v>73164986</v>
       </c>
       <c r="B6" t="n">
-        <v>96183</v>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomodon longifolius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schleich. ex Brid.) Hartm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711023</v>
+        <v>710998</v>
       </c>
       <c r="R6" t="n">
-        <v>6631245</v>
+        <v>6631300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,27 +1227,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266777</t>
+          <t>https://artportalen.se/Sighting/73164986</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73164369</v>
+        <v>121266777</v>
       </c>
       <c r="B7" t="n">
-        <v>96231</v>
+        <v>96183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>2674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Liten baronmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon longifolius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Schleich. ex Brid.) Hartm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>710872</v>
+        <v>711023</v>
       </c>
       <c r="R7" t="n">
-        <v>6631136</v>
+        <v>6631245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,12 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,24 +1329,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164369</t>
+          <t>https://artportalen.se/Sighting/121266777</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73164985</v>
+        <v>73164369</v>
       </c>
       <c r="B8" t="n">
         <v>96231</v>
@@ -1352,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>710996</v>
+        <v>710872</v>
       </c>
       <c r="R8" t="n">
-        <v>6631301</v>
+        <v>6631136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,13 +1442,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164985</t>
+          <t>https://artportalen.se/Sighting/73164369</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73165002</v>
+        <v>73164985</v>
       </c>
       <c r="B9" t="n">
         <v>96231</v>
@@ -1454,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>710974</v>
+        <v>710996</v>
       </c>
       <c r="R9" t="n">
-        <v>6631159</v>
+        <v>6631301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,16 +1544,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165002</t>
+          <t>https://artportalen.se/Sighting/73164985</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73165018</v>
+        <v>73165002</v>
       </c>
       <c r="B10" t="n">
-        <v>96338</v>
+        <v>96231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>710689</v>
+        <v>710974</v>
       </c>
       <c r="R10" t="n">
-        <v>6631191</v>
+        <v>6631159</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,13 +1646,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165018</t>
+          <t>https://artportalen.se/Sighting/73165002</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73165032</v>
+        <v>73165018</v>
       </c>
       <c r="B11" t="n">
         <v>96338</v>
@@ -1658,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>710582</v>
+        <v>710689</v>
       </c>
       <c r="R11" t="n">
-        <v>6631217</v>
+        <v>6631191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,16 +1748,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165032</t>
+          <t>https://artportalen.se/Sighting/73165018</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121266802</v>
+        <v>73165032</v>
       </c>
       <c r="B12" t="n">
-        <v>96458</v>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711034</v>
+        <v>710582</v>
       </c>
       <c r="R12" t="n">
-        <v>6631240</v>
+        <v>6631217</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,12 +1819,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,27 +1839,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266802</t>
+          <t>https://artportalen.se/Sighting/73165032</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1155679</v>
+        <v>121266802</v>
       </c>
       <c r="B13" t="n">
-        <v>92497</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,37 +1867,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N om Norra Kaffeberget, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>710578</v>
+        <v>711034</v>
       </c>
       <c r="R13" t="n">
-        <v>6631359</v>
+        <v>6631240</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,49 +1921,44 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Liten fd betad backe med ädellövskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1155679</t>
+          <t>https://artportalen.se/Sighting/121266802</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73165037</v>
+        <v>1155679</v>
       </c>
       <c r="B14" t="n">
         <v>92497</v>
@@ -1965,17 +1989,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>N om Norra Kaffeberget, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710535</v>
+        <v>710578</v>
       </c>
       <c r="R14" t="n">
-        <v>6631271</v>
+        <v>6631359</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,44 +2023,49 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Liten fd betad backe med ädellövskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165037</t>
+          <t>https://artportalen.se/Sighting/1155679</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73165038</v>
+        <v>73165037</v>
       </c>
       <c r="B15" t="n">
         <v>92497</v>
@@ -2071,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710538</v>
+        <v>710535</v>
       </c>
       <c r="R15" t="n">
-        <v>6631307</v>
+        <v>6631271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,13 +2161,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165038</t>
+          <t>https://artportalen.se/Sighting/73165037</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121266753</v>
+        <v>73165038</v>
       </c>
       <c r="B16" t="n">
         <v>92497</v>
@@ -2173,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711029</v>
+        <v>710538</v>
       </c>
       <c r="R16" t="n">
-        <v>6631264</v>
+        <v>6631307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,12 +2232,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,24 +2252,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266753</t>
+          <t>https://artportalen.se/Sighting/73165038</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121266754</v>
+        <v>121266753</v>
       </c>
       <c r="B17" t="n">
         <v>92497</v>
@@ -2275,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711032</v>
+        <v>711029</v>
       </c>
       <c r="R17" t="n">
-        <v>6631223</v>
+        <v>6631264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,38 +2365,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266754</t>
+          <t>https://artportalen.se/Sighting/121266753</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73165027</v>
+        <v>121266754</v>
       </c>
       <c r="B18" t="n">
-        <v>91930</v>
+        <v>92497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710559</v>
+        <v>711032</v>
       </c>
       <c r="R18" t="n">
-        <v>6631112</v>
+        <v>6631223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,12 +2436,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,27 +2456,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165027</t>
+          <t>https://artportalen.se/Sighting/121266754</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73164988</v>
+        <v>73165027</v>
       </c>
       <c r="B19" t="n">
-        <v>91867</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,21 +2484,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710950</v>
+        <v>710559</v>
       </c>
       <c r="R19" t="n">
-        <v>6631296</v>
+        <v>6631112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,38 +2569,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164988</t>
+          <t>https://artportalen.se/Sighting/73165027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73164362</v>
+        <v>73164988</v>
       </c>
       <c r="B20" t="n">
-        <v>79707</v>
+        <v>91867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6431</v>
+        <v>5445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2610,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710977</v>
+        <v>710950</v>
       </c>
       <c r="R20" t="n">
-        <v>6631206</v>
+        <v>6631296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,13 +2671,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164362</t>
+          <t>https://artportalen.se/Sighting/73164988</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73164384</v>
+        <v>73164362</v>
       </c>
       <c r="B21" t="n">
         <v>79707</v>
@@ -2683,10 +2712,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710700</v>
+        <v>710977</v>
       </c>
       <c r="R21" t="n">
-        <v>6631158</v>
+        <v>6631206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,13 +2773,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164384</t>
+          <t>https://artportalen.se/Sighting/73164362</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73165021</v>
+        <v>73164384</v>
       </c>
       <c r="B22" t="n">
         <v>79707</v>
@@ -2785,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>710703</v>
+        <v>710700</v>
       </c>
       <c r="R22" t="n">
-        <v>6631145</v>
+        <v>6631158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,38 +2875,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165021</t>
+          <t>https://artportalen.se/Sighting/73164384</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>73165026</v>
+        <v>73165021</v>
       </c>
       <c r="B23" t="n">
-        <v>80432</v>
+        <v>79707</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6431</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2916,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>710752</v>
+        <v>710703</v>
       </c>
       <c r="R23" t="n">
-        <v>6631090</v>
+        <v>6631145</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,13 +2977,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165026</t>
+          <t>https://artportalen.se/Sighting/73165021</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73165028</v>
+        <v>73165026</v>
       </c>
       <c r="B24" t="n">
         <v>80432</v>
@@ -2989,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>710597</v>
+        <v>710752</v>
       </c>
       <c r="R24" t="n">
-        <v>6631190</v>
+        <v>6631090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,13 +3079,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165028</t>
+          <t>https://artportalen.se/Sighting/73165026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73165029</v>
+        <v>73165028</v>
       </c>
       <c r="B25" t="n">
         <v>80432</v>
@@ -3091,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>710596</v>
+        <v>710597</v>
       </c>
       <c r="R25" t="n">
-        <v>6631193</v>
+        <v>6631190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,13 +3181,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165029</t>
+          <t>https://artportalen.se/Sighting/73165028</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>73165035</v>
+        <v>73165029</v>
       </c>
       <c r="B26" t="n">
         <v>80432</v>
@@ -3193,10 +3222,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>710561</v>
+        <v>710596</v>
       </c>
       <c r="R26" t="n">
-        <v>6631231</v>
+        <v>6631193</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,13 +3283,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165035</t>
+          <t>https://artportalen.se/Sighting/73165029</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89897152</v>
+        <v>73165035</v>
       </c>
       <c r="B27" t="n">
         <v>80432</v>
@@ -3289,22 +3318,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sässön, Norrtälje, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>710569</v>
+        <v>710561</v>
       </c>
       <c r="R27" t="n">
-        <v>6631376</v>
+        <v>6631231</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3328,17 +3354,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På minst 5 träd. Lind och ek.</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,31 +3368,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89897152</t>
+          <t>https://artportalen.se/Sighting/73165035</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89897899</v>
+        <v>89897152</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3405,17 +3425,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kaffeberget, Sässön, Upl</t>
+          <t>Sässön, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>710556</v>
+        <v>710569</v>
       </c>
       <c r="R28" t="n">
-        <v>6631228</v>
+        <v>6631376</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3445,6 +3465,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På minst 5 träd. Lind och ek.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,13 +3496,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89897899</t>
+          <t>https://artportalen.se/Sighting/89897152</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>93540305</v>
+        <v>89897899</v>
       </c>
       <c r="B29" t="n">
         <v>80432</v>
@@ -3511,14 +3536,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffeberget, Upl</t>
+          <t>Kaffeberget, Sässön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>710556</v>
       </c>
       <c r="R29" t="n">
-        <v>6631376</v>
+        <v>6631228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,12 +3570,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3566,24 +3591,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Pelle Barkengren</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Pelle Barkengren</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93540305</t>
+          <t>https://artportalen.se/Sighting/89897899</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121172188</v>
+        <v>93540305</v>
       </c>
       <c r="B30" t="n">
         <v>80432</v>
@@ -3617,17 +3642,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sässön, Sässövägen, Upl</t>
+          <t>Kaffeberget, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>710563</v>
+        <v>710556</v>
       </c>
       <c r="R30" t="n">
-        <v>6631386</v>
+        <v>6631376</v>
       </c>
       <c r="S30" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3651,22 +3676,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3682,24 +3697,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Rigbäck</t>
+          <t>Pelle Barkengren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Rigbäck</t>
+          <t>Pelle Barkengren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121172188</t>
+          <t>https://artportalen.se/Sighting/93540305</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124637699</v>
+        <v>121172188</v>
       </c>
       <c r="B31" t="n">
         <v>80432</v>
@@ -3727,31 +3742,23 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sässön, betesmarken, Upl</t>
+          <t>Sässön, Sässövägen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>710569</v>
+        <v>710563</v>
       </c>
       <c r="R31" t="n">
-        <v>6631302</v>
+        <v>6631386</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3775,12 +3782,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3796,62 +3813,73 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Lars Rigbäck</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Lars Rigbäck</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124637699</t>
+          <t>https://artportalen.se/Sighting/121172188</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>73164366</v>
+        <v>124637699</v>
       </c>
       <c r="B32" t="n">
-        <v>83314</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6471</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sässön, betesmarken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>710933</v>
+        <v>710569</v>
       </c>
       <c r="R32" t="n">
-        <v>6631136</v>
+        <v>6631302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,12 +3906,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3892,30 +3920,31 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164366</t>
+          <t>https://artportalen.se/Sighting/124637699</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>73164367</v>
+        <v>73164366</v>
       </c>
       <c r="B33" t="n">
         <v>83314</v>
@@ -3950,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>710916</v>
+        <v>710933</v>
       </c>
       <c r="R33" t="n">
-        <v>6631188</v>
+        <v>6631136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4011,13 +4040,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164367</t>
+          <t>https://artportalen.se/Sighting/73164366</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73164370</v>
+        <v>73164367</v>
       </c>
       <c r="B34" t="n">
         <v>83314</v>
@@ -4052,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>710861</v>
+        <v>710916</v>
       </c>
       <c r="R34" t="n">
-        <v>6631154</v>
+        <v>6631188</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4113,13 +4142,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164370</t>
+          <t>https://artportalen.se/Sighting/73164367</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73164371</v>
+        <v>73164370</v>
       </c>
       <c r="B35" t="n">
         <v>83314</v>
@@ -4154,10 +4183,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>710809</v>
+        <v>710861</v>
       </c>
       <c r="R35" t="n">
-        <v>6631112</v>
+        <v>6631154</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4215,13 +4244,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164371</t>
+          <t>https://artportalen.se/Sighting/73164370</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>73164373</v>
+        <v>73164371</v>
       </c>
       <c r="B36" t="n">
         <v>83314</v>
@@ -4256,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>710804</v>
+        <v>710809</v>
       </c>
       <c r="R36" t="n">
-        <v>6631172</v>
+        <v>6631112</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4317,13 +4346,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164373</t>
+          <t>https://artportalen.se/Sighting/73164371</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>73164375</v>
+        <v>73164373</v>
       </c>
       <c r="B37" t="n">
         <v>83314</v>
@@ -4358,10 +4387,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>710778</v>
+        <v>710804</v>
       </c>
       <c r="R37" t="n">
-        <v>6631200</v>
+        <v>6631172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4419,13 +4448,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164375</t>
+          <t>https://artportalen.se/Sighting/73164373</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>73164377</v>
+        <v>73164375</v>
       </c>
       <c r="B38" t="n">
         <v>83314</v>
@@ -4460,10 +4489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>710695</v>
+        <v>710778</v>
       </c>
       <c r="R38" t="n">
-        <v>6631204</v>
+        <v>6631200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4521,13 +4550,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164377</t>
+          <t>https://artportalen.se/Sighting/73164375</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>73164379</v>
+        <v>73164377</v>
       </c>
       <c r="B39" t="n">
         <v>83314</v>
@@ -4562,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>710639</v>
+        <v>710695</v>
       </c>
       <c r="R39" t="n">
-        <v>6631200</v>
+        <v>6631204</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,13 +4652,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164379</t>
+          <t>https://artportalen.se/Sighting/73164377</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73164382</v>
+        <v>73164379</v>
       </c>
       <c r="B40" t="n">
         <v>83314</v>
@@ -4664,10 +4693,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>710689</v>
+        <v>710639</v>
       </c>
       <c r="R40" t="n">
-        <v>6631191</v>
+        <v>6631200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4725,13 +4754,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164382</t>
+          <t>https://artportalen.se/Sighting/73164379</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>73164385</v>
+        <v>73164382</v>
       </c>
       <c r="B41" t="n">
         <v>83314</v>
@@ -4766,10 +4795,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>710703</v>
+        <v>710689</v>
       </c>
       <c r="R41" t="n">
-        <v>6631145</v>
+        <v>6631191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4827,13 +4856,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164385</t>
+          <t>https://artportalen.se/Sighting/73164382</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73164386</v>
+        <v>73164385</v>
       </c>
       <c r="B42" t="n">
         <v>83314</v>
@@ -4868,10 +4897,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>710713</v>
+        <v>710703</v>
       </c>
       <c r="R42" t="n">
-        <v>6631144</v>
+        <v>6631145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4929,13 +4958,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164386</t>
+          <t>https://artportalen.se/Sighting/73164385</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>73164389</v>
+        <v>73164386</v>
       </c>
       <c r="B43" t="n">
         <v>83314</v>
@@ -4970,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>710677</v>
+        <v>710713</v>
       </c>
       <c r="R43" t="n">
-        <v>6631128</v>
+        <v>6631144</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5031,63 +5060,51 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164389</t>
+          <t>https://artportalen.se/Sighting/73164386</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119906500</v>
+        <v>73164389</v>
       </c>
       <c r="B44" t="n">
-        <v>56925</v>
+        <v>83314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100045</v>
+        <v>6471</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sessön, Långgarn, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>710481</v>
+        <v>710677</v>
       </c>
       <c r="R44" t="n">
-        <v>6631271</v>
+        <v>6631128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,22 +5131,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>07:20</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5144,44 +5151,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906500</t>
+          <t>https://artportalen.se/Sighting/73164389</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119906483</v>
+        <v>119906500</v>
       </c>
       <c r="B45" t="n">
-        <v>57966</v>
+        <v>56925</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100048</v>
+        <v>100045</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5198,7 +5205,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5256,11 +5263,6 @@
           <t>09:20</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fårhagen öster om vassområdet.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5284,33 +5286,33 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906483</t>
+          <t>https://artportalen.se/Sighting/119906500</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119906469</v>
+        <v>119906483</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5387,7 +5389,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Öster om.</t>
+          <t>Fårhagen öster om vassområdet.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5413,16 +5415,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906469</t>
+          <t>https://artportalen.se/Sighting/119906483</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119906499</v>
+        <v>119906469</v>
       </c>
       <c r="B47" t="n">
-        <v>57258</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,16 +5432,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5449,14 +5451,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5514,6 +5516,11 @@
           <t>09:20</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Öster om.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5537,16 +5544,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906499</t>
+          <t>https://artportalen.se/Sighting/119906469</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73164397</v>
+        <v>119906499</v>
       </c>
       <c r="B48" t="n">
-        <v>56895</v>
+        <v>57258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5554,16 +5561,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100088</v>
+        <v>100065</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5571,17 +5578,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Långgarn, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>710568</v>
+        <v>710481</v>
       </c>
       <c r="R48" t="n">
-        <v>6631228</v>
+        <v>6631271</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5608,12 +5627,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5628,44 +5657,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164397</t>
+          <t>https://artportalen.se/Sighting/119906499</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119906448</v>
+        <v>73164397</v>
       </c>
       <c r="B49" t="n">
-        <v>58424</v>
+        <v>56895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102624</v>
+        <v>100088</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5673,29 +5702,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sessön, Långgarn, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>710481</v>
+        <v>710568</v>
       </c>
       <c r="R49" t="n">
-        <v>6631271</v>
+        <v>6631228</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5722,27 +5739,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>07:20</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>4-5.</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5757,62 +5759,74 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906448</t>
+          <t>https://artportalen.se/Sighting/73164397</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73165020</v>
+        <v>119906448</v>
       </c>
       <c r="B50" t="n">
-        <v>57947</v>
+        <v>58424</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102977</v>
+        <v>102624</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Långgarn, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>710700</v>
+        <v>710481</v>
       </c>
       <c r="R50" t="n">
-        <v>6631158</v>
+        <v>6631271</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5839,12 +5853,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>4-5.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5859,24 +5888,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165020</t>
+          <t>https://artportalen.se/Sighting/119906448</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119906457</v>
+        <v>73165020</v>
       </c>
       <c r="B51" t="n">
         <v>57947</v>
@@ -5904,29 +5933,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sessön, Långgarn, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>710481</v>
+        <v>710700</v>
       </c>
       <c r="R51" t="n">
-        <v>6631271</v>
+        <v>6631158</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5953,27 +5970,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>07:20</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Norr om.</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5988,44 +5990,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906457</t>
+          <t>https://artportalen.se/Sighting/73165020</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119906497</v>
+        <v>119906457</v>
       </c>
       <c r="B52" t="n">
-        <v>58209</v>
+        <v>57947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102980</v>
+        <v>102977</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6042,7 +6044,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6100,6 +6102,11 @@
           <t>09:20</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Norr om.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6123,16 +6130,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906497</t>
+          <t>https://artportalen.se/Sighting/119906457</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119906505</v>
+        <v>119906497</v>
       </c>
       <c r="B53" t="n">
-        <v>58497</v>
+        <v>58209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6140,33 +6147,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102990</v>
+        <v>102980</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6247,33 +6254,33 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906505</t>
+          <t>https://artportalen.se/Sighting/119906497</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73164396</v>
+        <v>119906505</v>
       </c>
       <c r="B54" t="n">
-        <v>58327</v>
+        <v>58497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6281,17 +6288,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Långgarn, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>710582</v>
+        <v>710481</v>
       </c>
       <c r="R54" t="n">
-        <v>6631217</v>
+        <v>6631271</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6318,12 +6337,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6338,27 +6367,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164396</t>
+          <t>https://artportalen.se/Sighting/119906505</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102494021</v>
+        <v>73164396</v>
       </c>
       <c r="B55" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,53 +6395,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ekbacke, Sessön, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>710568</v>
+        <v>710582</v>
       </c>
       <c r="R55" t="n">
-        <v>6631383</v>
+        <v>6631217</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6436,22 +6449,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6466,77 +6469,81 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102494021</t>
+          <t>https://artportalen.se/Sighting/73164396</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119906506</v>
+        <v>102494021</v>
       </c>
       <c r="B56" t="n">
-        <v>58112</v>
+        <v>58439</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sessön, Långgarn, Upl</t>
+          <t>Ekbacke, Sessön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>710481</v>
+        <v>710568</v>
       </c>
       <c r="R56" t="n">
-        <v>6631271</v>
+        <v>6631383</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6560,22 +6567,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6601,38 +6608,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906506</t>
+          <t>https://artportalen.se/Sighting/102494021</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119906596</v>
+        <v>119906506</v>
       </c>
       <c r="B57" t="n">
-        <v>58353</v>
+        <v>58112</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103037</v>
+        <v>103020</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6644,7 +6651,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6725,16 +6732,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906596</t>
+          <t>https://artportalen.se/Sighting/119906506</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119906490</v>
+        <v>119906596</v>
       </c>
       <c r="B58" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6742,33 +6749,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6849,33 +6856,33 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906490</t>
+          <t>https://artportalen.se/Sighting/119906596</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119906495</v>
+        <v>119906490</v>
       </c>
       <c r="B59" t="n">
-        <v>58649</v>
+        <v>58602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103057</v>
+        <v>103042</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6885,12 +6892,16 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6946,11 +6957,6 @@
           <t>09:20</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6974,16 +6980,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906495</t>
+          <t>https://artportalen.se/Sighting/119906490</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119906540</v>
+        <v>119906495</v>
       </c>
       <c r="B60" t="n">
-        <v>58085</v>
+        <v>58649</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6991,26 +6997,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -7071,6 +7077,11 @@
           <t>09:20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7094,66 +7105,62 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119906540</t>
+          <t>https://artportalen.se/Sighting/119906495</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>89897531</v>
+        <v>119906540</v>
       </c>
       <c r="B61" t="n">
-        <v>56689</v>
+        <v>58085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206046</v>
+        <v>205976</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sässön, Norrtälje, Upl</t>
+          <t>Sessön, Långgarn, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>710569</v>
+        <v>710481</v>
       </c>
       <c r="R61" t="n">
-        <v>6631376</v>
+        <v>6631271</v>
       </c>
       <c r="S61" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7177,12 +7184,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7197,74 +7214,77 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89897531</t>
+          <t>https://artportalen.se/Sighting/119906540</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2196319</v>
+        <v>89897531</v>
       </c>
       <c r="B62" t="n">
-        <v>107609</v>
+        <v>56689</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219686</v>
+        <v>206046</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>N om Norra Kaffeberget, Upl</t>
+          <t>Sässön, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>710578</v>
+        <v>710569</v>
       </c>
       <c r="R62" t="n">
-        <v>6631359</v>
+        <v>6631376</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7288,12 +7308,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7304,33 +7324,28 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Liten fd betad backe med ädellövskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2196319</t>
+          <t>https://artportalen.se/Sighting/89897531</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>73164352</v>
+        <v>2196319</v>
       </c>
       <c r="B63" t="n">
         <v>107609</v>
@@ -7358,20 +7373,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>N om Norra Kaffeberget, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>710953</v>
+        <v>710578</v>
       </c>
       <c r="R63" t="n">
-        <v>6631291</v>
+        <v>6631359</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7395,12 +7419,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7411,28 +7435,33 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Liten fd betad backe med ädellövskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164352</t>
+          <t>https://artportalen.se/Sighting/2196319</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121266820</v>
+        <v>73164352</v>
       </c>
       <c r="B64" t="n">
         <v>107609</v>
@@ -7467,10 +7496,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>711031</v>
+        <v>710953</v>
       </c>
       <c r="R64" t="n">
-        <v>6631247</v>
+        <v>6631291</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7497,12 +7526,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7517,24 +7546,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266820</t>
+          <t>https://artportalen.se/Sighting/73164352</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121266821</v>
+        <v>121266820</v>
       </c>
       <c r="B65" t="n">
         <v>107609</v>
@@ -7569,10 +7598,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>711013</v>
+        <v>711031</v>
       </c>
       <c r="R65" t="n">
-        <v>6631251</v>
+        <v>6631247</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7630,65 +7659,51 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266821</t>
+          <t>https://artportalen.se/Sighting/121266820</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2454567</v>
+        <v>121266821</v>
       </c>
       <c r="B66" t="n">
-        <v>99059</v>
+        <v>107609</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219792</v>
+        <v>219686</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sessön, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>710509</v>
+        <v>711013</v>
       </c>
       <c r="R66" t="n">
-        <v>6631414</v>
+        <v>6631251</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7715,12 +7730,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2006-06-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2006-06-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7731,71 +7746,80 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>I kanten av lövskogsbacke</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2454567</t>
+          <t>https://artportalen.se/Sighting/121266821</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>73164353</v>
+        <v>2454567</v>
       </c>
       <c r="B67" t="n">
-        <v>106813</v>
+        <v>99059</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220785</v>
+        <v>219792</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>711032</v>
+        <v>710509</v>
       </c>
       <c r="R67" t="n">
-        <v>6631242</v>
+        <v>6631414</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7822,12 +7846,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2006-06-02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2006-06-02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7838,28 +7862,33 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>I kanten av lövskogsbacke</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164353</t>
+          <t>https://artportalen.se/Sighting/2454567</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>73164354</v>
+        <v>73164353</v>
       </c>
       <c r="B68" t="n">
         <v>106813</v>
@@ -7894,10 +7923,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>711033</v>
+        <v>711032</v>
       </c>
       <c r="R68" t="n">
-        <v>6631247</v>
+        <v>6631242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7955,13 +7984,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164354</t>
+          <t>https://artportalen.se/Sighting/73164353</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>73164355</v>
+        <v>73164354</v>
       </c>
       <c r="B69" t="n">
         <v>106813</v>
@@ -7996,10 +8025,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>711004</v>
+        <v>711033</v>
       </c>
       <c r="R69" t="n">
-        <v>6631277</v>
+        <v>6631247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8057,13 +8086,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164355</t>
+          <t>https://artportalen.se/Sighting/73164354</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>73164356</v>
+        <v>73164355</v>
       </c>
       <c r="B70" t="n">
         <v>106813</v>
@@ -8098,10 +8127,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>711012</v>
+        <v>711004</v>
       </c>
       <c r="R70" t="n">
-        <v>6631278</v>
+        <v>6631277</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8159,13 +8188,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164356</t>
+          <t>https://artportalen.se/Sighting/73164355</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73164357</v>
+        <v>73164356</v>
       </c>
       <c r="B71" t="n">
         <v>106813</v>
@@ -8200,10 +8229,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>711022</v>
+        <v>711012</v>
       </c>
       <c r="R71" t="n">
-        <v>6631239</v>
+        <v>6631278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8261,13 +8290,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164357</t>
+          <t>https://artportalen.se/Sighting/73164356</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>73164358</v>
+        <v>73164357</v>
       </c>
       <c r="B72" t="n">
         <v>106813</v>
@@ -8302,10 +8331,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>710960</v>
+        <v>711022</v>
       </c>
       <c r="R72" t="n">
-        <v>6631242</v>
+        <v>6631239</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8363,13 +8392,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164358</t>
+          <t>https://artportalen.se/Sighting/73164357</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>73164359</v>
+        <v>73164358</v>
       </c>
       <c r="B73" t="n">
         <v>106813</v>
@@ -8404,10 +8433,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>710964</v>
+        <v>710960</v>
       </c>
       <c r="R73" t="n">
-        <v>6631231</v>
+        <v>6631242</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8465,13 +8494,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164359</t>
+          <t>https://artportalen.se/Sighting/73164358</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73164360</v>
+        <v>73164359</v>
       </c>
       <c r="B74" t="n">
         <v>106813</v>
@@ -8506,10 +8535,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>710965</v>
+        <v>710964</v>
       </c>
       <c r="R74" t="n">
-        <v>6631224</v>
+        <v>6631231</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8567,13 +8596,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164360</t>
+          <t>https://artportalen.se/Sighting/73164359</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>73164363</v>
+        <v>73164360</v>
       </c>
       <c r="B75" t="n">
         <v>106813</v>
@@ -8608,10 +8637,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>711021</v>
+        <v>710965</v>
       </c>
       <c r="R75" t="n">
-        <v>6631187</v>
+        <v>6631224</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8669,13 +8698,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164363</t>
+          <t>https://artportalen.se/Sighting/73164360</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>73164364</v>
+        <v>73164363</v>
       </c>
       <c r="B76" t="n">
         <v>106813</v>
@@ -8710,10 +8739,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>711011</v>
+        <v>711021</v>
       </c>
       <c r="R76" t="n">
-        <v>6631189</v>
+        <v>6631187</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8771,13 +8800,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164364</t>
+          <t>https://artportalen.se/Sighting/73164363</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>73164365</v>
+        <v>73164364</v>
       </c>
       <c r="B77" t="n">
         <v>106813</v>
@@ -8812,10 +8841,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>710974</v>
+        <v>711011</v>
       </c>
       <c r="R77" t="n">
-        <v>6631159</v>
+        <v>6631189</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8873,13 +8902,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164365</t>
+          <t>https://artportalen.se/Sighting/73164364</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>73164368</v>
+        <v>73164365</v>
       </c>
       <c r="B78" t="n">
         <v>106813</v>
@@ -8914,10 +8943,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>710892</v>
+        <v>710974</v>
       </c>
       <c r="R78" t="n">
-        <v>6631125</v>
+        <v>6631159</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8975,13 +9004,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164368</t>
+          <t>https://artportalen.se/Sighting/73164365</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>73164372</v>
+        <v>73164368</v>
       </c>
       <c r="B79" t="n">
         <v>106813</v>
@@ -9016,10 +9045,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>710832</v>
+        <v>710892</v>
       </c>
       <c r="R79" t="n">
-        <v>6631167</v>
+        <v>6631125</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9077,13 +9106,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164372</t>
+          <t>https://artportalen.se/Sighting/73164368</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>73164374</v>
+        <v>73164372</v>
       </c>
       <c r="B80" t="n">
         <v>106813</v>
@@ -9118,10 +9147,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>710805</v>
+        <v>710832</v>
       </c>
       <c r="R80" t="n">
-        <v>6631173</v>
+        <v>6631167</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9179,13 +9208,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164374</t>
+          <t>https://artportalen.se/Sighting/73164372</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>73164376</v>
+        <v>73164374</v>
       </c>
       <c r="B81" t="n">
         <v>106813</v>
@@ -9220,10 +9249,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>710745</v>
+        <v>710805</v>
       </c>
       <c r="R81" t="n">
-        <v>6631172</v>
+        <v>6631173</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9281,13 +9310,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164376</t>
+          <t>https://artportalen.se/Sighting/73164374</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>73164378</v>
+        <v>73164376</v>
       </c>
       <c r="B82" t="n">
         <v>106813</v>
@@ -9322,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>710654</v>
+        <v>710745</v>
       </c>
       <c r="R82" t="n">
-        <v>6631215</v>
+        <v>6631172</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9383,13 +9412,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164378</t>
+          <t>https://artportalen.se/Sighting/73164376</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>73164380</v>
+        <v>73164378</v>
       </c>
       <c r="B83" t="n">
         <v>106813</v>
@@ -9424,10 +9453,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>710643</v>
+        <v>710654</v>
       </c>
       <c r="R83" t="n">
-        <v>6631198</v>
+        <v>6631215</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9485,13 +9514,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164380</t>
+          <t>https://artportalen.se/Sighting/73164378</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>73164383</v>
+        <v>73164380</v>
       </c>
       <c r="B84" t="n">
         <v>106813</v>
@@ -9526,10 +9555,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>710703</v>
+        <v>710643</v>
       </c>
       <c r="R84" t="n">
-        <v>6631167</v>
+        <v>6631198</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9587,13 +9616,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164383</t>
+          <t>https://artportalen.se/Sighting/73164380</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>73164387</v>
+        <v>73164383</v>
       </c>
       <c r="B85" t="n">
         <v>106813</v>
@@ -9628,10 +9657,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>710701</v>
+        <v>710703</v>
       </c>
       <c r="R85" t="n">
-        <v>6631136</v>
+        <v>6631167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9689,13 +9718,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164387</t>
+          <t>https://artportalen.se/Sighting/73164383</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>73164390</v>
+        <v>73164387</v>
       </c>
       <c r="B86" t="n">
         <v>106813</v>
@@ -9730,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>710734</v>
+        <v>710701</v>
       </c>
       <c r="R86" t="n">
-        <v>6631114</v>
+        <v>6631136</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9791,13 +9820,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164390</t>
+          <t>https://artportalen.se/Sighting/73164387</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>73164399</v>
+        <v>73164390</v>
       </c>
       <c r="B87" t="n">
         <v>106813</v>
@@ -9832,10 +9861,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>710535</v>
+        <v>710734</v>
       </c>
       <c r="R87" t="n">
-        <v>6631247</v>
+        <v>6631114</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9893,13 +9922,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164399</t>
+          <t>https://artportalen.se/Sighting/73164390</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>73164400</v>
+        <v>73164399</v>
       </c>
       <c r="B88" t="n">
         <v>106813</v>
@@ -9937,7 +9966,7 @@
         <v>710535</v>
       </c>
       <c r="R88" t="n">
-        <v>6631271</v>
+        <v>6631247</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9995,13 +10024,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164400</t>
+          <t>https://artportalen.se/Sighting/73164399</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>73164401</v>
+        <v>73164400</v>
       </c>
       <c r="B89" t="n">
         <v>106813</v>
@@ -10036,10 +10065,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>710538</v>
+        <v>710535</v>
       </c>
       <c r="R89" t="n">
-        <v>6631307</v>
+        <v>6631271</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10097,13 +10126,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164401</t>
+          <t>https://artportalen.se/Sighting/73164400</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>73164402</v>
+        <v>73164401</v>
       </c>
       <c r="B90" t="n">
         <v>106813</v>
@@ -10138,10 +10167,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>710536</v>
+        <v>710538</v>
       </c>
       <c r="R90" t="n">
-        <v>6631309</v>
+        <v>6631307</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10199,13 +10228,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164402</t>
+          <t>https://artportalen.se/Sighting/73164401</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>73164987</v>
+        <v>73164402</v>
       </c>
       <c r="B91" t="n">
         <v>106813</v>
@@ -10240,10 +10269,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>710979</v>
+        <v>710536</v>
       </c>
       <c r="R91" t="n">
-        <v>6631310</v>
+        <v>6631309</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10301,13 +10330,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164987</t>
+          <t>https://artportalen.se/Sighting/73164402</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>83429727</v>
+        <v>73164987</v>
       </c>
       <c r="B92" t="n">
         <v>106813</v>
@@ -10335,24 +10364,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>288, 30000176, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>710566</v>
+        <v>710979</v>
       </c>
       <c r="R92" t="n">
-        <v>6631459</v>
+        <v>6631310</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10374,19 +10399,14 @@
           <t>Norrtälje</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>4DDC9AAA-6A51-4AE0-81FA-3025ECEC2213</t>
-        </is>
-      </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2007-07-19</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2007-07-19</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10401,28 +10421,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83429727</t>
+          <t>https://artportalen.se/Sighting/73164987</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>110518495</v>
+        <v>83429727</v>
       </c>
       <c r="B93" t="n">
         <v>106813</v>
@@ -10457,17 +10473,17 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>288, 30000176, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>710613</v>
+        <v>710566</v>
       </c>
       <c r="R93" t="n">
-        <v>6631327</v>
+        <v>6631459</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10491,22 +10507,17 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>4ba1d95d-756f-496b-9188-be570edc4d36</t>
+          <t>4DDC9AAA-6A51-4AE0-81FA-3025ECEC2213</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Stamkvistning.</t>
+          <t>2007-07-19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10521,7 +10532,7 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Miguel Jaramillo</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -10531,18 +10542,18 @@
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110518495</t>
+          <t>https://artportalen.se/Sighting/83429727</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>110518497</v>
+        <v>110518495</v>
       </c>
       <c r="B94" t="n">
         <v>106813</v>
@@ -10581,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>710576</v>
+        <v>710613</v>
       </c>
       <c r="R94" t="n">
-        <v>6631424</v>
+        <v>6631327</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10611,7 +10622,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>613b5f35-736f-4a16-9510-f14070278fa9</t>
+          <t>4ba1d95d-756f-496b-9188-be570edc4d36</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -10656,13 +10667,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110518497</t>
+          <t>https://artportalen.se/Sighting/110518495</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110518499</v>
+        <v>110518497</v>
       </c>
       <c r="B95" t="n">
         <v>106813</v>
@@ -10701,10 +10712,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>710588</v>
+        <v>710576</v>
       </c>
       <c r="R95" t="n">
-        <v>6631408</v>
+        <v>6631424</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10731,7 +10742,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>e5db2bf3-3aeb-4033-a94b-a24252841918</t>
+          <t>613b5f35-736f-4a16-9510-f14070278fa9</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -10776,13 +10787,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110518499</t>
+          <t>https://artportalen.se/Sighting/110518497</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>110585907</v>
+        <v>110518499</v>
       </c>
       <c r="B96" t="n">
         <v>106813</v>
@@ -10821,10 +10832,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>710572</v>
+        <v>710588</v>
       </c>
       <c r="R96" t="n">
-        <v>6631455</v>
+        <v>6631408</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10851,7 +10862,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>b5f804e8-4070-4f66-9f71-07c0df76caaf</t>
+          <t>e5db2bf3-3aeb-4033-a94b-a24252841918</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -10862,6 +10873,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Stamkvistning.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10891,13 +10907,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110585907</t>
+          <t>https://artportalen.se/Sighting/110518499</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>110469654</v>
+        <v>110585907</v>
       </c>
       <c r="B97" t="n">
         <v>106813</v>
@@ -10936,10 +10952,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>710557</v>
+        <v>710572</v>
       </c>
       <c r="R97" t="n">
-        <v>6631468</v>
+        <v>6631455</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10966,7 +10982,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>e5966832-2fb2-451c-8a41-a4990b3a7108</t>
+          <t>b5f804e8-4070-4f66-9f71-07c0df76caaf</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -10977,11 +10993,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11011,13 +11022,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110469654</t>
+          <t>https://artportalen.se/Sighting/110585907</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>110507418</v>
+        <v>110469654</v>
       </c>
       <c r="B98" t="n">
         <v>106813</v>
@@ -11056,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>710567</v>
+        <v>710557</v>
       </c>
       <c r="R98" t="n">
-        <v>6631459</v>
+        <v>6631468</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11086,7 +11097,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>7e5d038b-1a34-4c9f-bdef-861fbbf64696</t>
+          <t>e5966832-2fb2-451c-8a41-a4990b3a7108</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -11131,13 +11142,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110507418</t>
+          <t>https://artportalen.se/Sighting/110469654</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121198727</v>
+        <v>110507418</v>
       </c>
       <c r="B99" t="n">
         <v>106813</v>
@@ -11165,20 +11176,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>711023</v>
+        <v>710567</v>
       </c>
       <c r="R99" t="n">
-        <v>6631244</v>
+        <v>6631459</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11200,14 +11215,24 @@
           <t>Norrtälje</t>
         </is>
       </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>7e5d038b-1a34-4c9f-bdef-861fbbf64696</t>
+        </is>
+      </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11222,24 +11247,28 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121198727</t>
+          <t>https://artportalen.se/Sighting/110507418</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121266705</v>
+        <v>121198727</v>
       </c>
       <c r="B100" t="n">
         <v>106813</v>
@@ -11274,10 +11303,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>711030</v>
+        <v>711023</v>
       </c>
       <c r="R100" t="n">
-        <v>6631240</v>
+        <v>6631244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11335,54 +11364,54 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266705</t>
+          <t>https://artportalen.se/Sighting/121198727</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3907293</v>
+        <v>121266705</v>
       </c>
       <c r="B101" t="n">
-        <v>102241</v>
+        <v>106813</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221235</v>
+        <v>220785</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sessön, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>710670</v>
+        <v>711030</v>
       </c>
       <c r="R101" t="n">
-        <v>6631199</v>
+        <v>6631240</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11406,12 +11435,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2001-06-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2001-06-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11422,33 +11451,28 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Lövträdsrik granskogsbacke</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3907293</t>
+          <t>https://artportalen.se/Sighting/121266705</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>73165017</v>
+        <v>3907293</v>
       </c>
       <c r="B102" t="n">
         <v>102241</v>
@@ -11479,17 +11503,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>710643</v>
+        <v>710670</v>
       </c>
       <c r="R102" t="n">
-        <v>6631198</v>
+        <v>6631199</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11513,12 +11537,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2001-06-14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2001-06-14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11529,28 +11553,33 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Lövträdsrik granskogsbacke</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165017</t>
+          <t>https://artportalen.se/Sighting/3907293</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>73165039</v>
+        <v>73165017</v>
       </c>
       <c r="B103" t="n">
         <v>102241</v>
@@ -11585,10 +11614,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>710536</v>
+        <v>710643</v>
       </c>
       <c r="R103" t="n">
-        <v>6631309</v>
+        <v>6631198</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11646,54 +11675,54 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165039</t>
+          <t>https://artportalen.se/Sighting/73165017</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5028616</v>
+        <v>73165039</v>
       </c>
       <c r="B104" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>N om Norra Kaffeberget, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>710578</v>
+        <v>710536</v>
       </c>
       <c r="R104" t="n">
-        <v>6631359</v>
+        <v>6631309</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11717,12 +11746,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>1992-04-28</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11733,33 +11762,28 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>Liten fd betad backe med ädellövskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5028616</t>
+          <t>https://artportalen.se/Sighting/73165039</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>73164347</v>
+        <v>5028616</v>
       </c>
       <c r="B105" t="n">
         <v>101326</v>
@@ -11790,17 +11814,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>N om Norra Kaffeberget, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>710996</v>
+        <v>710578</v>
       </c>
       <c r="R105" t="n">
-        <v>6631301</v>
+        <v>6631359</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11824,12 +11848,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11840,28 +11864,33 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Liten fd betad backe med ädellövskog</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164347</t>
+          <t>https://artportalen.se/Sighting/5028616</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>73164349</v>
+        <v>73164347</v>
       </c>
       <c r="B106" t="n">
         <v>101326</v>
@@ -11896,10 +11925,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>710998</v>
+        <v>710996</v>
       </c>
       <c r="R106" t="n">
-        <v>6631300</v>
+        <v>6631301</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11957,13 +11986,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164349</t>
+          <t>https://artportalen.se/Sighting/73164347</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>73164351</v>
+        <v>73164349</v>
       </c>
       <c r="B107" t="n">
         <v>101326</v>
@@ -11998,10 +12027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>710950</v>
+        <v>710998</v>
       </c>
       <c r="R107" t="n">
-        <v>6631296</v>
+        <v>6631300</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12059,13 +12088,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164351</t>
+          <t>https://artportalen.se/Sighting/73164349</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>73164393</v>
+        <v>73164351</v>
       </c>
       <c r="B108" t="n">
         <v>101326</v>
@@ -12100,10 +12129,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>710597</v>
+        <v>710950</v>
       </c>
       <c r="R108" t="n">
-        <v>6631190</v>
+        <v>6631296</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12161,13 +12190,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164393</t>
+          <t>https://artportalen.se/Sighting/73164351</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>73164394</v>
+        <v>73164393</v>
       </c>
       <c r="B109" t="n">
         <v>101326</v>
@@ -12202,10 +12231,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>710596</v>
+        <v>710597</v>
       </c>
       <c r="R109" t="n">
-        <v>6631193</v>
+        <v>6631190</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12263,13 +12292,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164394</t>
+          <t>https://artportalen.se/Sighting/73164393</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>73164395</v>
+        <v>73164394</v>
       </c>
       <c r="B110" t="n">
         <v>101326</v>
@@ -12304,10 +12333,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>710579</v>
+        <v>710596</v>
       </c>
       <c r="R110" t="n">
-        <v>6631219</v>
+        <v>6631193</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12365,13 +12394,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164395</t>
+          <t>https://artportalen.se/Sighting/73164394</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>73164398</v>
+        <v>73164395</v>
       </c>
       <c r="B111" t="n">
         <v>101326</v>
@@ -12406,10 +12435,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>710561</v>
+        <v>710579</v>
       </c>
       <c r="R111" t="n">
-        <v>6631231</v>
+        <v>6631219</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12467,13 +12496,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164398</t>
+          <t>https://artportalen.se/Sighting/73164395</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>73164992</v>
+        <v>73164398</v>
       </c>
       <c r="B112" t="n">
         <v>101326</v>
@@ -12508,10 +12537,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>711004</v>
+        <v>710561</v>
       </c>
       <c r="R112" t="n">
-        <v>6631277</v>
+        <v>6631231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12569,13 +12598,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164992</t>
+          <t>https://artportalen.se/Sighting/73164398</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>73164995</v>
+        <v>73164992</v>
       </c>
       <c r="B113" t="n">
         <v>101326</v>
@@ -12610,10 +12639,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>710960</v>
+        <v>711004</v>
       </c>
       <c r="R113" t="n">
-        <v>6631242</v>
+        <v>6631277</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12671,13 +12700,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164995</t>
+          <t>https://artportalen.se/Sighting/73164992</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>73164998</v>
+        <v>73164995</v>
       </c>
       <c r="B114" t="n">
         <v>101326</v>
@@ -12712,10 +12741,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>711020</v>
+        <v>710960</v>
       </c>
       <c r="R114" t="n">
-        <v>6631217</v>
+        <v>6631242</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12773,13 +12802,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164998</t>
+          <t>https://artportalen.se/Sighting/73164995</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>73164999</v>
+        <v>73164998</v>
       </c>
       <c r="B115" t="n">
         <v>101326</v>
@@ -12814,10 +12843,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>710977</v>
+        <v>711020</v>
       </c>
       <c r="R115" t="n">
-        <v>6631206</v>
+        <v>6631217</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12875,13 +12904,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164999</t>
+          <t>https://artportalen.se/Sighting/73164998</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>73165000</v>
+        <v>73164999</v>
       </c>
       <c r="B116" t="n">
         <v>101326</v>
@@ -12916,10 +12945,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>711021</v>
+        <v>710977</v>
       </c>
       <c r="R116" t="n">
-        <v>6631187</v>
+        <v>6631206</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12977,13 +13006,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165000</t>
+          <t>https://artportalen.se/Sighting/73164999</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>73165003</v>
+        <v>73165000</v>
       </c>
       <c r="B117" t="n">
         <v>101326</v>
@@ -13018,10 +13047,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>710933</v>
+        <v>711021</v>
       </c>
       <c r="R117" t="n">
-        <v>6631136</v>
+        <v>6631187</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13079,13 +13108,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165003</t>
+          <t>https://artportalen.se/Sighting/73165000</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>73165008</v>
+        <v>73165003</v>
       </c>
       <c r="B118" t="n">
         <v>101326</v>
@@ -13120,10 +13149,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>710809</v>
+        <v>710933</v>
       </c>
       <c r="R118" t="n">
-        <v>6631112</v>
+        <v>6631136</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13181,13 +13210,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165008</t>
+          <t>https://artportalen.se/Sighting/73165003</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>73165009</v>
+        <v>73165008</v>
       </c>
       <c r="B119" t="n">
         <v>101326</v>
@@ -13222,10 +13251,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>710832</v>
+        <v>710809</v>
       </c>
       <c r="R119" t="n">
-        <v>6631167</v>
+        <v>6631112</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13283,13 +13312,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165009</t>
+          <t>https://artportalen.se/Sighting/73165008</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>73165016</v>
+        <v>73165009</v>
       </c>
       <c r="B120" t="n">
         <v>101326</v>
@@ -13324,10 +13353,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>710639</v>
+        <v>710832</v>
       </c>
       <c r="R120" t="n">
-        <v>6631200</v>
+        <v>6631167</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13385,13 +13414,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165016</t>
+          <t>https://artportalen.se/Sighting/73165009</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>73165023</v>
+        <v>73165016</v>
       </c>
       <c r="B121" t="n">
         <v>101326</v>
@@ -13426,10 +13455,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>710701</v>
+        <v>710639</v>
       </c>
       <c r="R121" t="n">
-        <v>6631136</v>
+        <v>6631200</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13487,13 +13516,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165023</t>
+          <t>https://artportalen.se/Sighting/73165016</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>73165025</v>
+        <v>73165023</v>
       </c>
       <c r="B122" t="n">
         <v>101326</v>
@@ -13528,10 +13557,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>710734</v>
+        <v>710701</v>
       </c>
       <c r="R122" t="n">
-        <v>6631114</v>
+        <v>6631136</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13589,13 +13618,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165025</t>
+          <t>https://artportalen.se/Sighting/73165023</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>73165040</v>
+        <v>73165025</v>
       </c>
       <c r="B123" t="n">
         <v>101326</v>
@@ -13630,10 +13659,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>710536</v>
+        <v>710734</v>
       </c>
       <c r="R123" t="n">
-        <v>6631309</v>
+        <v>6631114</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13691,13 +13720,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165040</t>
+          <t>https://artportalen.se/Sighting/73165025</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>108606242</v>
+        <v>73165040</v>
       </c>
       <c r="B124" t="n">
         <v>101326</v>
@@ -13726,27 +13755,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sässön, Norrtälje, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>710569</v>
+        <v>710536</v>
       </c>
       <c r="R124" t="n">
-        <v>6631376</v>
+        <v>6631309</v>
       </c>
       <c r="S124" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13770,12 +13791,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13784,31 +13805,30 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Micael Söderman, Frida Skagerberg</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108606242</t>
+          <t>https://artportalen.se/Sighting/73165040</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>115698139</v>
+        <v>108606242</v>
       </c>
       <c r="B125" t="n">
         <v>101326</v>
@@ -13837,19 +13857,27 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sässön, Upl</t>
+          <t>Sässön, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>710703</v>
+        <v>710569</v>
       </c>
       <c r="R125" t="n">
-        <v>6631053</v>
+        <v>6631376</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13873,12 +13901,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13887,30 +13915,31 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anna  Engqvist</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anna  Engqvist</t>
+          <t>Micael Söderman, Frida Skagerberg</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115698139</t>
+          <t>https://artportalen.se/Sighting/108606242</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121266727</v>
+        <v>115698139</v>
       </c>
       <c r="B126" t="n">
         <v>101326</v>
@@ -13941,14 +13970,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sässön, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>711006</v>
+        <v>710703</v>
       </c>
       <c r="R126" t="n">
-        <v>6631252</v>
+        <v>6631053</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13975,12 +14004,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13995,24 +14024,24 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Anna  Engqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Anna  Engqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266727</t>
+          <t>https://artportalen.se/Sighting/115698139</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121266728</v>
+        <v>121266727</v>
       </c>
       <c r="B127" t="n">
         <v>101326</v>
@@ -14047,10 +14076,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>711012</v>
+        <v>711006</v>
       </c>
       <c r="R127" t="n">
-        <v>6631273</v>
+        <v>6631252</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14108,16 +14137,16 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266728</t>
+          <t>https://artportalen.se/Sighting/121266727</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>5260754</v>
+        <v>121266728</v>
       </c>
       <c r="B128" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14125,37 +14154,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sessön, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>710670</v>
+        <v>711012</v>
       </c>
       <c r="R128" t="n">
-        <v>6631199</v>
+        <v>6631273</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14179,12 +14208,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2001-06-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2001-06-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14195,33 +14224,28 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>Lövträdsrik granskogsbacke</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5260754</t>
+          <t>https://artportalen.se/Sighting/121266728</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>73165014</v>
+        <v>5260754</v>
       </c>
       <c r="B129" t="n">
         <v>101228</v>
@@ -14252,17 +14276,17 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Sessön, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>710695</v>
+        <v>710670</v>
       </c>
       <c r="R129" t="n">
-        <v>6631204</v>
+        <v>6631199</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14286,12 +14310,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2001-06-14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
+          <t>2001-06-14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14302,28 +14326,33 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>Lövträdsrik granskogsbacke</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165014</t>
+          <t>https://artportalen.se/Sighting/5260754</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>73165015</v>
+        <v>73165014</v>
       </c>
       <c r="B130" t="n">
         <v>101228</v>
@@ -14358,10 +14387,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>710654</v>
+        <v>710695</v>
       </c>
       <c r="R130" t="n">
-        <v>6631215</v>
+        <v>6631204</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14419,38 +14448,38 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165015</t>
+          <t>https://artportalen.se/Sighting/73165014</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>73164361</v>
+        <v>73165015</v>
       </c>
       <c r="B131" t="n">
-        <v>103403</v>
+        <v>101228</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14460,10 +14489,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>711020</v>
+        <v>710654</v>
       </c>
       <c r="R131" t="n">
-        <v>6631217</v>
+        <v>6631215</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14521,13 +14550,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164361</t>
+          <t>https://artportalen.se/Sighting/73165015</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>73164994</v>
+        <v>73164361</v>
       </c>
       <c r="B132" t="n">
         <v>103403</v>
@@ -14562,10 +14591,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>711022</v>
+        <v>711020</v>
       </c>
       <c r="R132" t="n">
-        <v>6631239</v>
+        <v>6631217</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14623,13 +14652,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73164994</t>
+          <t>https://artportalen.se/Sighting/73164361</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>73165010</v>
+        <v>73164994</v>
       </c>
       <c r="B133" t="n">
         <v>103403</v>
@@ -14664,10 +14693,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>710804</v>
+        <v>711022</v>
       </c>
       <c r="R133" t="n">
-        <v>6631172</v>
+        <v>6631239</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14725,13 +14754,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73165010</t>
+          <t>https://artportalen.se/Sighting/73164994</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121266796</v>
+        <v>73165010</v>
       </c>
       <c r="B134" t="n">
         <v>103403</v>
@@ -14766,10 +14795,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>711037</v>
+        <v>710804</v>
       </c>
       <c r="R134" t="n">
-        <v>6631273</v>
+        <v>6631172</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14796,12 +14825,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14816,24 +14845,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Adam Trapp</t>
+          <t>Daniel Segerlind, Kajsa Mattsson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266796</t>
+          <t>https://artportalen.se/Sighting/73165010</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121266797</v>
+        <v>121266796</v>
       </c>
       <c r="B135" t="n">
         <v>103403</v>
@@ -14868,10 +14897,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>711039</v>
+        <v>711037</v>
       </c>
       <c r="R135" t="n">
-        <v>6631262</v>
+        <v>6631273</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14929,38 +14958,38 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266797</t>
+          <t>https://artportalen.se/Sighting/121266796</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121266810</v>
+        <v>121266797</v>
       </c>
       <c r="B136" t="n">
-        <v>80357</v>
+        <v>103403</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6003719</v>
+        <v>223246</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14970,10 +14999,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>711022</v>
+        <v>711039</v>
       </c>
       <c r="R136" t="n">
-        <v>6631244</v>
+        <v>6631262</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15031,16 +15060,16 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266810</t>
+          <t>https://artportalen.se/Sighting/121266797</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121266778</v>
+        <v>121266810</v>
       </c>
       <c r="B137" t="n">
-        <v>96183</v>
+        <v>80357</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15048,21 +15077,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2674</v>
+        <v>6003719</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Liten baronmossa</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Anomodon longifolius</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schleich. ex Brid.) Hartm.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15072,10 +15101,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>711062</v>
+        <v>711022</v>
       </c>
       <c r="R137" t="n">
-        <v>6631220</v>
+        <v>6631244</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15102,12 +15131,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15133,58 +15162,54 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121266778</t>
+          <t>https://artportalen.se/Sighting/121266810</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>83432775</v>
+        <v>121266778</v>
       </c>
       <c r="B138" t="n">
-        <v>106813</v>
+        <v>96183</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220785</v>
+        <v>2674</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liten baronmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anomodon longifolius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schleich. ex Brid.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>291, 30000255, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>711056</v>
+        <v>711062</v>
       </c>
       <c r="R138" t="n">
-        <v>6631209</v>
+        <v>6631220</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15206,19 +15231,14 @@
           <t>Norrtälje</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>62515EA7-600F-4BF8-A7FA-D40EC4CEE1AC</t>
-        </is>
-      </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2007-07-20</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2007-07-20</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15233,28 +15253,24 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
+          <t>Adam Trapp</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Adam Trapp</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83432775</t>
+          <t>https://artportalen.se/Sighting/121266778</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>110467510</v>
+        <v>83432775</v>
       </c>
       <c r="B139" t="n">
         <v>106813</v>
@@ -15289,17 +15305,17 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>291, 30000255, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
         <v>711056</v>
       </c>
       <c r="R139" t="n">
-        <v>6631210</v>
+        <v>6631209</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15323,22 +15339,17 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>ed4602df-2443-4876-9539-6e5f0862b007</t>
+          <t>62515EA7-600F-4BF8-A7FA-D40EC4CEE1AC</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-20</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
+          <t>2007-07-20</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15353,20 +15364,140 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83432775</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>110467510</v>
+      </c>
+      <c r="B140" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Norrtälje kommun, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>711056</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6631210</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>ed4602df-2443-4876-9539-6e5f0862b007</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
           <t>Julia Stigenberg</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
+      <c r="AX140" t="inlineStr">
         <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AY139" t="inlineStr">
+      <c r="AY140" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
+      <c r="AZ140" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110467510</t>
         </is>
@@ -15512,6 +15643,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88605</v>
+        <v>88607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88607</v>
+        <v>88609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88609</v>
+        <v>88610</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88610</v>
+        <v>88616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88616</v>
+        <v>88620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88620</v>
+        <v>88622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88622</v>
+        <v>88635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88635</v>
+        <v>88637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -828,11 +828,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgarn, Upl</t>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88637</v>
+        <v>88640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88640</v>
+        <v>88650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88650</v>
+        <v>88651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88654</v>
+        <v>88659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88659</v>
+        <v>88670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136875884</v>
       </c>
       <c r="B3" t="n">
-        <v>88670</v>
+        <v>88671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137513390</v>
       </c>
       <c r="B5" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137513392</v>
       </c>
       <c r="B6" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137513403</v>
       </c>
       <c r="B7" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137513397</v>
       </c>
       <c r="B14" t="n">
-        <v>96543</v>
+        <v>96546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>137522562</v>
       </c>
       <c r="B23" t="n">
-        <v>92243</v>
+        <v>92246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>137513391</v>
       </c>
       <c r="B29" t="n">
-        <v>81194</v>
+        <v>81197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>137513393</v>
       </c>
       <c r="B30" t="n">
-        <v>81194</v>
+        <v>81197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
